--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -884,22 +884,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -916,22 +919,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>15.15</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -948,22 +954,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.5</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -980,22 +989,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1012,22 +1024,25 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.9</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1044,22 +1059,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1076,22 +1094,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1108,22 +1129,25 @@
         <v>33</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>51.52</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5.9</v>
       </c>
       <c r="J19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -2365,22 +2389,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>90.63</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
+      </c>
+      <c r="I12" s="2">
+        <v>7.5</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2397,22 +2424,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>15.15</v>
+      </c>
+      <c r="I13" s="2">
+        <v>7.9</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2429,22 +2459,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.5</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2461,22 +2494,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I15" s="2">
+        <v>6.9</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2493,22 +2529,25 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I16" s="2">
+        <v>6.9</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2525,22 +2564,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>96.88</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>3.13</v>
+      </c>
+      <c r="I17" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2557,22 +2599,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>8</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>25</v>
+      </c>
+      <c r="I18" s="2">
+        <v>7.6</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>3.13</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2589,22 +2634,25 @@
         <v>33</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F19">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>48.48</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>51.52</v>
+      </c>
+      <c r="I19" s="2">
+        <v>5.9</v>
       </c>
       <c r="J19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -680,22 +680,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -782,22 +785,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2185,22 +2191,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>7.9</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -2287,22 +2296,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>64.52</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>35.48</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.7</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>35.48</v>
       </c>
     </row>
     <row r="10" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -750,25 +750,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H8" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
       <c r="I8" s="2">
         <v>7.9</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2261,25 +2261,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G8" s="1">
-        <v>84.84999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="H8" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
       <c r="I8" s="2">
         <v>7.9</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K8" s="1">
-        <v>15.15</v>
+        <v>12.12</v>
       </c>
     </row>
     <row r="9" spans="1:11">

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -540,25 +540,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -575,25 +575,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -610,25 +610,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -645,25 +645,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1327,22 +1327,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I2" s="2">
+        <v>9.5</v>
       </c>
       <c r="J2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1359,22 +1362,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J3">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1391,22 +1397,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I4" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J4">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1423,22 +1432,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I5" s="2">
+        <v>9.199999999999999</v>
       </c>
       <c r="J5">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1519,22 +1531,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>63.64</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>36.36</v>
+      </c>
+      <c r="I8" s="2">
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>33</v>
+        <v>11</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>33.33</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1583,22 +1598,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>26.32</v>
+      </c>
+      <c r="I10" s="2">
+        <v>8.800000000000001</v>
       </c>
       <c r="J10">
-        <v>38</v>
+        <v>10</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>26.32</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2051,25 +2069,25 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H2" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I2" s="2">
         <v>9.5</v>
       </c>
       <c r="J2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -2086,25 +2104,25 @@
         <v>32</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I3" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -2121,25 +2139,25 @@
         <v>38</v>
       </c>
       <c r="E4">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>84.20999999999999</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.5</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -2156,25 +2174,25 @@
         <v>31</v>
       </c>
       <c r="E5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
-        <v>90.31999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -2261,16 +2279,16 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>15.15</v>
       </c>
       <c r="I8" s="2">
         <v>7.9</v>
@@ -2343,7 +2361,7 @@
         <v>15.79</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8.6</v>
       </c>
       <c r="J10">
         <v>6</v>

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -715,25 +715,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H7" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -855,25 +855,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>83.87</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>16.13</v>
+        <v>12.9</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -890,25 +890,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -925,25 +925,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H13" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -972,13 +972,13 @@
         <v>35.48</v>
       </c>
       <c r="I14" s="2">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>26.32</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>26.32</v>
       </c>
       <c r="I16" s="2">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1065,25 +1065,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
         <v>8.800000000000001</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1100,25 +1100,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G18" s="1">
-        <v>75</v>
+        <v>78.13</v>
       </c>
       <c r="H18" s="1">
-        <v>25</v>
+        <v>21.88</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>30.56</v>
       </c>
       <c r="I21" s="2">
-        <v>6.7</v>
+        <v>6.6</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1240,25 +1240,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" s="1">
-        <v>64.52</v>
+        <v>70.97</v>
       </c>
       <c r="H22" s="1">
-        <v>35.48</v>
+        <v>29.03</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1467,22 +1467,25 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I6" s="2">
+        <v>8.5</v>
       </c>
       <c r="J6">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1499,22 +1502,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="F7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>69.44</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>30.56</v>
+      </c>
+      <c r="I7" s="2">
+        <v>8.6</v>
       </c>
       <c r="J7">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1566,22 +1572,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>61.29</v>
+      </c>
+      <c r="I9" s="2">
+        <v>7.4</v>
       </c>
       <c r="J9">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1633,22 +1642,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>38.71</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>61.29</v>
+      </c>
+      <c r="I11" s="2">
+        <v>8.4</v>
       </c>
       <c r="J11">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>61.29</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1665,22 +1677,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I12" s="2">
+        <v>8.4</v>
       </c>
       <c r="J12">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1697,22 +1712,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>90.91</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>9.09</v>
+      </c>
+      <c r="I13" s="2">
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1729,22 +1747,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>61.29</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>38.71</v>
+      </c>
+      <c r="I14" s="2">
+        <v>6.1</v>
       </c>
       <c r="J14">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1761,22 +1782,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>31.58</v>
+      </c>
+      <c r="I15" s="2">
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1793,22 +1817,25 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>0</v>
+        <v>68.42</v>
       </c>
       <c r="H16" s="1">
-        <v>100</v>
+        <v>31.58</v>
+      </c>
+      <c r="I16" s="2">
+        <v>7.1</v>
       </c>
       <c r="J16">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1825,22 +1852,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I17" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J17">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1857,22 +1887,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>100</v>
+        <v>0</v>
+      </c>
+      <c r="I18" s="2">
+        <v>9.699999999999999</v>
       </c>
       <c r="J18">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1889,22 +1922,25 @@
         <v>33</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0</v>
+        <v>96.97</v>
       </c>
       <c r="H19" s="1">
-        <v>100</v>
+        <v>3.03</v>
+      </c>
+      <c r="I19" s="2">
+        <v>9.300000000000001</v>
       </c>
       <c r="J19">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K19" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1921,22 +1957,25 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>32</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="H20" s="1">
-        <v>100</v>
+        <v>12.5</v>
+      </c>
+      <c r="I20" s="2">
+        <v>7.5</v>
       </c>
       <c r="J20">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K20" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1953,22 +1992,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1">
-        <v>0</v>
+        <v>63.89</v>
       </c>
       <c r="H21" s="1">
-        <v>100</v>
+        <v>36.11</v>
+      </c>
+      <c r="I21" s="2">
+        <v>6.6</v>
       </c>
       <c r="J21">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1985,22 +2027,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>0</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>100</v>
+        <v>32.26</v>
+      </c>
+      <c r="I22" s="2">
+        <v>6.4</v>
       </c>
       <c r="J22">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2221,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2244,25 +2289,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G7" s="1">
-        <v>66.67</v>
+        <v>77.78</v>
       </c>
       <c r="H7" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
       <c r="I7" s="2">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="K7" s="1">
-        <v>33.33</v>
+        <v>22.22</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2326,7 +2371,7 @@
         <v>35.48</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
         <v>11</v>
@@ -2384,25 +2429,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>83.87</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K11" s="1">
-        <v>16.13</v>
+        <v>9.68</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2419,25 +2464,25 @@
         <v>32</v>
       </c>
       <c r="E12">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>9.380000000000001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -2454,25 +2499,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G13" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H13" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
       <c r="I13" s="2">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K13" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2489,25 +2534,25 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14" s="1">
-        <v>64.52</v>
+        <v>61.29</v>
       </c>
       <c r="H14" s="1">
-        <v>35.48</v>
+        <v>38.71</v>
       </c>
       <c r="I14" s="2">
-        <v>6.5</v>
+        <v>6.2</v>
       </c>
       <c r="J14">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -2524,25 +2569,25 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G15" s="1">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H15" s="1">
-        <v>26.32</v>
+        <v>31.58</v>
       </c>
       <c r="I15" s="2">
         <v>6.9</v>
       </c>
       <c r="J15">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -2559,25 +2604,25 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="1">
-        <v>73.68000000000001</v>
+        <v>68.42</v>
       </c>
       <c r="H16" s="1">
-        <v>26.32</v>
+        <v>31.58</v>
       </c>
       <c r="I16" s="2">
         <v>6.9</v>
       </c>
       <c r="J16">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" s="1">
-        <v>5.26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -2594,25 +2639,25 @@
         <v>32</v>
       </c>
       <c r="E17">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G17" s="1">
-        <v>96.88</v>
+        <v>100</v>
       </c>
       <c r="H17" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K17" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -2629,25 +2674,25 @@
         <v>32</v>
       </c>
       <c r="E18">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="F18">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G18" s="1">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H18" s="1">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>7.6</v>
+        <v>8.9</v>
       </c>
       <c r="J18">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K18" s="1">
-        <v>3.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -2664,19 +2709,19 @@
         <v>33</v>
       </c>
       <c r="E19">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="F19">
-        <v>17</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>48.48</v>
+        <v>96.97</v>
       </c>
       <c r="H19" s="1">
-        <v>51.52</v>
+        <v>3.03</v>
       </c>
       <c r="I19" s="2">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="J19">
         <v>0</v>
@@ -2699,19 +2744,19 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F20">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G20" s="1">
-        <v>65.63</v>
+        <v>87.5</v>
       </c>
       <c r="H20" s="1">
-        <v>34.38</v>
+        <v>12.5</v>
       </c>
       <c r="I20" s="2">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2734,25 +2779,25 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F21">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G21" s="1">
-        <v>69.44</v>
+        <v>63.89</v>
       </c>
       <c r="H21" s="1">
-        <v>30.56</v>
+        <v>36.11</v>
       </c>
       <c r="I21" s="2">
         <v>6.7</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -2769,25 +2814,25 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F22">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G22" s="1">
-        <v>64.52</v>
+        <v>67.73999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>35.48</v>
+        <v>32.26</v>
       </c>
       <c r="I22" s="2">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="J22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K22" s="1">
-        <v>6.45</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -1537,25 +1537,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F8">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="1">
-        <v>63.64</v>
+        <v>66.67</v>
       </c>
       <c r="H8" s="1">
-        <v>36.36</v>
+        <v>33.33</v>
       </c>
       <c r="I8" s="2">
         <v>8</v>
       </c>
       <c r="J8">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K8" s="1">
-        <v>33.33</v>
+        <v>30.3</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1572,25 +1572,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="1">
-        <v>38.71</v>
+        <v>41.94</v>
       </c>
       <c r="H9" s="1">
-        <v>61.29</v>
+        <v>58.06</v>
       </c>
       <c r="I9" s="2">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="J9">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K9" s="1">
-        <v>61.29</v>
+        <v>58.06</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1642,25 +1642,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="F11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G11" s="1">
-        <v>38.71</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H11" s="1">
-        <v>61.29</v>
+        <v>12.9</v>
       </c>
       <c r="I11" s="2">
         <v>8.4</v>
       </c>
       <c r="J11">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="K11" s="1">
-        <v>61.29</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2441,7 +2441,7 @@
         <v>9.68</v>
       </c>
       <c r="I11" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J11">
         <v>3</v>

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -715,25 +715,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H7" s="1">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.300000000000001</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>22.22</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -750,25 +750,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F8">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G8" s="1">
-        <v>87.88</v>
+        <v>93.94</v>
       </c>
       <c r="H8" s="1">
-        <v>12.12</v>
+        <v>6.06</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -820,25 +820,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="1">
-        <v>84.20999999999999</v>
+        <v>86.84</v>
       </c>
       <c r="H10" s="1">
-        <v>15.79</v>
+        <v>13.16</v>
       </c>
       <c r="I10" s="2">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -855,25 +855,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G11" s="1">
-        <v>87.09999999999999</v>
+        <v>93.55</v>
       </c>
       <c r="H11" s="1">
-        <v>12.9</v>
+        <v>6.45</v>
       </c>
       <c r="I11" s="2">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1502,25 +1502,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>69.44</v>
+        <v>88.89</v>
       </c>
       <c r="H7" s="1">
-        <v>30.56</v>
+        <v>11.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.6</v>
+        <v>7.8</v>
       </c>
       <c r="J7">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>30.56</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1537,25 +1537,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="F8">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>66.67</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="H8" s="1">
-        <v>33.33</v>
+        <v>21.21</v>
       </c>
       <c r="I8" s="2">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K8" s="1">
-        <v>30.3</v>
+        <v>15.15</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1607,25 +1607,25 @@
         <v>38</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F10">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>73.68000000000001</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H10" s="1">
-        <v>26.32</v>
+        <v>15.79</v>
       </c>
       <c r="I10" s="2">
-        <v>8.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>26.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1642,25 +1642,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>87.09999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H11" s="1">
-        <v>12.9</v>
+        <v>3.23</v>
       </c>
       <c r="I11" s="2">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
       <c r="J11">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>12.9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1689,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1724,7 +1724,7 @@
         <v>9.09</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -2196,7 +2196,7 @@
         <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>9.300000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="I5" s="2">
-        <v>9.4</v>
+        <v>9.5</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -2266,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="I6" s="2">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -2289,25 +2289,25 @@
         <v>36</v>
       </c>
       <c r="E7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G7" s="1">
-        <v>77.78</v>
+        <v>88.89</v>
       </c>
       <c r="H7" s="1">
-        <v>22.22</v>
+        <v>11.11</v>
       </c>
       <c r="I7" s="2">
-        <v>8.4</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K7" s="1">
-        <v>22.22</v>
+        <v>2.78</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2324,25 +2324,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G8" s="1">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H8" s="1">
-        <v>15.15</v>
+        <v>9.09</v>
       </c>
       <c r="I8" s="2">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
       <c r="J8">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>12.12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -2406,13 +2406,13 @@
         <v>15.79</v>
       </c>
       <c r="I10" s="2">
-        <v>8.6</v>
+        <v>7.9</v>
       </c>
       <c r="J10">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>15.79</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -2429,25 +2429,25 @@
         <v>31</v>
       </c>
       <c r="E11">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G11" s="1">
-        <v>90.31999999999999</v>
+        <v>96.77</v>
       </c>
       <c r="H11" s="1">
-        <v>9.68</v>
+        <v>3.23</v>
       </c>
       <c r="I11" s="2">
-        <v>8.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="J11">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>9.68</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2511,7 +2511,7 @@
         <v>9.09</v>
       </c>
       <c r="I13" s="2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
         <v>3</v>
@@ -2744,19 +2744,19 @@
         <v>32</v>
       </c>
       <c r="E20">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="F20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G20" s="1">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H20" s="1">
-        <v>12.5</v>
+        <v>6.25</v>
       </c>
       <c r="I20" s="2">
-        <v>7.2</v>
+        <v>7.5</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2779,19 +2779,19 @@
         <v>36</v>
       </c>
       <c r="E21">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="F21">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="G21" s="1">
-        <v>63.89</v>
+        <v>86.11</v>
       </c>
       <c r="H21" s="1">
-        <v>36.11</v>
+        <v>13.89</v>
       </c>
       <c r="I21" s="2">
-        <v>6.7</v>
+        <v>7.1</v>
       </c>
       <c r="J21">
         <v>0</v>
@@ -2814,16 +2814,16 @@
         <v>31</v>
       </c>
       <c r="E22">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F22">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="G22" s="1">
-        <v>67.73999999999999</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="H22" s="1">
-        <v>32.26</v>
+        <v>12.9</v>
       </c>
       <c r="I22" s="2">
         <v>6.6</v>

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -2534,19 +2534,19 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G14" s="1">
-        <v>61.29</v>
+        <v>74.19</v>
       </c>
       <c r="H14" s="1">
-        <v>38.71</v>
+        <v>25.81</v>
       </c>
       <c r="I14" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J14">
         <v>0</v>

--- a/academias/Electricidad - Estadisticos 20212.xlsx
+++ b/academias/Electricidad - Estadisticos 20212.xlsx
@@ -730,10 +730,10 @@
         <v>7.7</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -785,25 +785,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>64.52</v>
+        <v>77.42</v>
       </c>
       <c r="H9" s="1">
-        <v>35.48</v>
+        <v>22.58</v>
       </c>
       <c r="I9" s="2">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -925,25 +925,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H13" s="1">
-        <v>9.09</v>
+        <v>3.03</v>
       </c>
       <c r="I13" s="2">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1514,13 +1514,13 @@
         <v>11.11</v>
       </c>
       <c r="I7" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1537,25 +1537,25 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="1">
-        <v>78.79000000000001</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>21.21</v>
+        <v>18.18</v>
       </c>
       <c r="I8" s="2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>15.15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1572,25 +1572,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F9">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="G9" s="1">
-        <v>41.94</v>
+        <v>77.42</v>
       </c>
       <c r="H9" s="1">
-        <v>58.06</v>
+        <v>22.58</v>
       </c>
       <c r="I9" s="2">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="J9">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>58.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1712,25 +1712,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H13" s="1">
-        <v>9.09</v>
+        <v>3.03</v>
       </c>
       <c r="I13" s="2">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2304,10 +2304,10 @@
         <v>7.7</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>2.78</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -2324,19 +2324,19 @@
         <v>33</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G8" s="1">
-        <v>90.91</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H8" s="1">
-        <v>9.09</v>
+        <v>15.15</v>
       </c>
       <c r="I8" s="2">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2359,25 +2359,25 @@
         <v>31</v>
       </c>
       <c r="E9">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F9">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="G9" s="1">
-        <v>64.52</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="H9" s="1">
-        <v>35.48</v>
+        <v>19.35</v>
       </c>
       <c r="I9" s="2">
-        <v>7.6</v>
+        <v>6.9</v>
       </c>
       <c r="J9">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>35.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -2476,7 +2476,7 @@
         <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -2499,25 +2499,25 @@
         <v>33</v>
       </c>
       <c r="E13">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F13">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G13" s="1">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H13" s="1">
-        <v>9.09</v>
+        <v>3.03</v>
       </c>
       <c r="I13" s="2">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>9.09</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -2569,19 +2569,19 @@
         <v>19</v>
       </c>
       <c r="E15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G15" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H15" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I15" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -2604,19 +2604,19 @@
         <v>19</v>
       </c>
       <c r="E16">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G16" s="1">
-        <v>68.42</v>
+        <v>78.95</v>
       </c>
       <c r="H16" s="1">
-        <v>31.58</v>
+        <v>21.05</v>
       </c>
       <c r="I16" s="2">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="J16">
         <v>0</v>
@@ -2651,7 +2651,7 @@
         <v>0</v>
       </c>
       <c r="I17" s="2">
-        <v>9.4</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2686,7 +2686,7 @@
         <v>0</v>
       </c>
       <c r="I18" s="2">
-        <v>8.9</v>
+        <v>9</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2709,19 +2709,19 @@
         <v>33</v>
       </c>
       <c r="E19">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F19">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G19" s="1">
-        <v>96.97</v>
+        <v>90.91</v>
       </c>
       <c r="H19" s="1">
-        <v>3.03</v>
+        <v>9.09</v>
       </c>
       <c r="I19" s="2">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="J19">
         <v>0</v>
